--- a/artfynd/A 16473-2021 artfynd.xlsx
+++ b/artfynd/A 16473-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 16473-2021 artfynd.xlsx
+++ b/artfynd/A 16473-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1763,6 +1763,312 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129281156</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91533</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vidingsjö O, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>538918</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6469861</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Landeryd</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Barrskog med inslag av ek, hassel, björk mm</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Monica Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Monica Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129281157</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92233</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vidingsjö O, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>538918</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6469861</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Landeryd</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Barrskog med inslag av ek, hassel, björk mm</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Monica Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Monica Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129281093</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92301</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>366</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kandelabersvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Artomyces pyxidatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vidingsjö O, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>539068</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6469803</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Landeryd</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Ek, hassel, björk med inslag av gran och tall</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Monica Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Monica Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16473-2021 artfynd.xlsx
+++ b/artfynd/A 16473-2021 artfynd.xlsx
@@ -1765,32 +1765,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129281156</v>
+        <v>129281157</v>
       </c>
       <c r="B11" t="n">
-        <v>91533</v>
+        <v>92240</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1867,32 +1867,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129281157</v>
+        <v>129281156</v>
       </c>
       <c r="B12" t="n">
-        <v>92233</v>
+        <v>91540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1972,7 +1972,7 @@
         <v>129281093</v>
       </c>
       <c r="B13" t="n">
-        <v>92301</v>
+        <v>92308</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16473-2021 artfynd.xlsx
+++ b/artfynd/A 16473-2021 artfynd.xlsx
@@ -1768,7 +1768,7 @@
         <v>129281157</v>
       </c>
       <c r="B11" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>129281156</v>
       </c>
       <c r="B12" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>129281093</v>
       </c>
       <c r="B13" t="n">
-        <v>92308</v>
+        <v>92310</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16473-2021 artfynd.xlsx
+++ b/artfynd/A 16473-2021 artfynd.xlsx
@@ -1765,32 +1765,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129281157</v>
+        <v>129281156</v>
       </c>
       <c r="B11" t="n">
-        <v>92242</v>
+        <v>91542</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1867,32 +1867,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129281156</v>
+        <v>129281157</v>
       </c>
       <c r="B12" t="n">
-        <v>91542</v>
+        <v>92242</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>

--- a/artfynd/A 16473-2021 artfynd.xlsx
+++ b/artfynd/A 16473-2021 artfynd.xlsx
@@ -1768,7 +1768,7 @@
         <v>129281156</v>
       </c>
       <c r="B11" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>129281157</v>
       </c>
       <c r="B12" t="n">
-        <v>92242</v>
+        <v>92257</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>129281093</v>
       </c>
       <c r="B13" t="n">
-        <v>92310</v>
+        <v>92324</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16473-2021 artfynd.xlsx
+++ b/artfynd/A 16473-2021 artfynd.xlsx
@@ -1870,7 +1870,7 @@
         <v>129281157</v>
       </c>
       <c r="B12" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>129281093</v>
       </c>
       <c r="B13" t="n">
-        <v>92324</v>
+        <v>92325</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16473-2021 artfynd.xlsx
+++ b/artfynd/A 16473-2021 artfynd.xlsx
@@ -1768,7 +1768,7 @@
         <v>129281156</v>
       </c>
       <c r="B11" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>129281157</v>
       </c>
       <c r="B12" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>129281093</v>
       </c>
       <c r="B13" t="n">
-        <v>92325</v>
+        <v>92328</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16473-2021 artfynd.xlsx
+++ b/artfynd/A 16473-2021 artfynd.xlsx
@@ -1768,7 +1768,7 @@
         <v>129281156</v>
       </c>
       <c r="B11" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>129281157</v>
       </c>
       <c r="B12" t="n">
-        <v>92261</v>
+        <v>92263</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>129281093</v>
       </c>
       <c r="B13" t="n">
-        <v>92328</v>
+        <v>92330</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16473-2021 artfynd.xlsx
+++ b/artfynd/A 16473-2021 artfynd.xlsx
@@ -1768,7 +1768,7 @@
         <v>129281156</v>
       </c>
       <c r="B11" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>129281157</v>
       </c>
       <c r="B12" t="n">
-        <v>92263</v>
+        <v>92267</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>129281093</v>
       </c>
       <c r="B13" t="n">
-        <v>92330</v>
+        <v>92334</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16473-2021 artfynd.xlsx
+++ b/artfynd/A 16473-2021 artfynd.xlsx
@@ -1768,7 +1768,7 @@
         <v>129281156</v>
       </c>
       <c r="B11" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>129281157</v>
       </c>
       <c r="B12" t="n">
-        <v>92267</v>
+        <v>92268</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>129281093</v>
       </c>
       <c r="B13" t="n">
-        <v>92334</v>
+        <v>92335</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16473-2021 artfynd.xlsx
+++ b/artfynd/A 16473-2021 artfynd.xlsx
@@ -1765,32 +1765,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129281156</v>
+        <v>129281157</v>
       </c>
       <c r="B11" t="n">
-        <v>91550</v>
+        <v>92268</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1867,32 +1867,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129281157</v>
+        <v>129281156</v>
       </c>
       <c r="B12" t="n">
-        <v>92268</v>
+        <v>91550</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>

--- a/artfynd/A 16473-2021 artfynd.xlsx
+++ b/artfynd/A 16473-2021 artfynd.xlsx
@@ -1765,32 +1765,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129281157</v>
+        <v>129281156</v>
       </c>
       <c r="B11" t="n">
-        <v>92268</v>
+        <v>91550</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1867,32 +1867,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129281156</v>
+        <v>129281157</v>
       </c>
       <c r="B12" t="n">
-        <v>91550</v>
+        <v>92268</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>

--- a/artfynd/A 16473-2021 artfynd.xlsx
+++ b/artfynd/A 16473-2021 artfynd.xlsx
@@ -1768,7 +1768,7 @@
         <v>129281156</v>
       </c>
       <c r="B11" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>129281157</v>
       </c>
       <c r="B12" t="n">
-        <v>92268</v>
+        <v>92271</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>129281093</v>
       </c>
       <c r="B13" t="n">
-        <v>92335</v>
+        <v>92338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16473-2021 artfynd.xlsx
+++ b/artfynd/A 16473-2021 artfynd.xlsx
@@ -1765,32 +1765,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129281156</v>
+        <v>129281157</v>
       </c>
       <c r="B11" t="n">
-        <v>91553</v>
+        <v>92271</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1867,32 +1867,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129281157</v>
+        <v>129281156</v>
       </c>
       <c r="B12" t="n">
-        <v>92271</v>
+        <v>91553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>

--- a/artfynd/A 16473-2021 artfynd.xlsx
+++ b/artfynd/A 16473-2021 artfynd.xlsx
@@ -1765,32 +1765,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129281157</v>
+        <v>129281156</v>
       </c>
       <c r="B11" t="n">
-        <v>92271</v>
+        <v>91553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1867,32 +1867,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129281156</v>
+        <v>129281157</v>
       </c>
       <c r="B12" t="n">
-        <v>91553</v>
+        <v>92271</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>

--- a/artfynd/A 16473-2021 artfynd.xlsx
+++ b/artfynd/A 16473-2021 artfynd.xlsx
@@ -1768,7 +1768,7 @@
         <v>129281157</v>
       </c>
       <c r="B11" t="n">
-        <v>92271</v>
+        <v>92299</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>129281156</v>
       </c>
       <c r="B12" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>129281093</v>
       </c>
       <c r="B13" t="n">
-        <v>92338</v>
+        <v>92366</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16473-2021 artfynd.xlsx
+++ b/artfynd/A 16473-2021 artfynd.xlsx
@@ -1765,32 +1765,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129281157</v>
+        <v>129281156</v>
       </c>
       <c r="B11" t="n">
-        <v>92299</v>
+        <v>91587</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1867,32 +1867,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129281156</v>
+        <v>129281157</v>
       </c>
       <c r="B12" t="n">
-        <v>91581</v>
+        <v>92305</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1972,7 +1972,7 @@
         <v>129281093</v>
       </c>
       <c r="B13" t="n">
-        <v>92366</v>
+        <v>92372</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 16473-2021 artfynd.xlsx
+++ b/artfynd/A 16473-2021 artfynd.xlsx
@@ -1765,32 +1765,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129281156</v>
+        <v>129281157</v>
       </c>
       <c r="B11" t="n">
-        <v>91587</v>
+        <v>92306</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1867,32 +1867,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129281157</v>
+        <v>129281156</v>
       </c>
       <c r="B12" t="n">
-        <v>92305</v>
+        <v>91588</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1972,7 +1972,7 @@
         <v>129281093</v>
       </c>
       <c r="B13" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
